--- a/data/burst.xlsx
+++ b/data/burst.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc6f98a884355999/pococha-burst-viewer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D78B91D5-9D9A-4799-ABA0-4F3F84B66666}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E22C95C-EB85-40B3-9E7B-857EEFC4353F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="0" windowWidth="22605" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22605" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">まとめ!$A$1:$B$1</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
   <si>
     <t>名前</t>
   </si>
@@ -1631,7 +1632,7 @@
     </row>
     <row r="98" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H98" s="1">
-        <f t="shared" ref="H98:H129" si="3">SUM(C98:G98)</f>
+        <f t="shared" ref="H98:H104" si="3">SUM(C98:G98)</f>
         <v>0</v>
       </c>
     </row>
@@ -1668,6 +1669,1136 @@
     <row r="104" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H104" s="1">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C66B7024-317A-4164-8C32-9B471BFAB393}">
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3">
+        <v>823469</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.14549999999999999</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.16689999999999999</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.1734</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:H65" si="0">SUM(C2:G2)</f>
+        <v>0.48580000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6733248</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.13339999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.159</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" si="0"/>
+        <v>0.43769999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>10616381</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.14280000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.1565</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.1764</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.1847</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.66039999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10365606</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.1459</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.58310000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9747604</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.1613</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.18509999999999999</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.66500000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11565389</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.12720000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.14990000000000001</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.40710000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10694690</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.14230000000000001</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.1618</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.1772</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.48130000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3857497</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.13850000000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.1585</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.1651</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.59760000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>4124528</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.1368</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.14810000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.58260000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10612747</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.13789999999999999</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.13850000000000001</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.43709999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11653960</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.56020000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9710497</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.13569999999999999</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.15590000000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.46160000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11105602</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.124</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.1477</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.16589999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5736</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9169434</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.1008</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.1011</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.12720000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.3291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8876201</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.15509999999999999</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.182</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.45710000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>11199606</v>
+      </c>
+      <c r="C17" s="1">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>8.9499999999999996E-2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.1024</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28310000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>10948387</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.1313</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.1489</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.1598</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="0"/>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>10762589</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.1013</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.14460000000000001</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.15559999999999999</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="0"/>
+        <v>0.40149999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4065090</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.13220000000000001</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.158</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="0"/>
+        <v>0.40860000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6324408</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.1212</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.1285</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.14269999999999999</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.39239999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11482694</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.11509999999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.1429</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.1482</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="0"/>
+        <v>0.40620000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11815209</v>
+      </c>
+      <c r="C23" s="1">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.13089999999999999</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.14549999999999999</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="0"/>
+        <v>0.37209999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="3">
+        <v>11375494</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.1191</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="0"/>
+        <v>0.38839999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="3">
+        <v>9465990</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.1053</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7.0800000000000002E-2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>9.0200000000000002E-2</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="0"/>
+        <v>0.26629999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="3">
+        <v>7007480</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.1038</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.1201</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.1002</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="0"/>
+        <v>0.3241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="3">
+        <v>11846339</v>
+      </c>
+      <c r="C27" s="1">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.11459999999999999</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.1318</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="0"/>
+        <v>0.34609999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="3">
+        <v>10588807</v>
+      </c>
+      <c r="C28" s="1">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.1021</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="0"/>
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11060330</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6.2100000000000002E-2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="0"/>
+        <v>0.17180000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2631043</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.1303</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.1303</v>
+      </c>
+      <c r="H30" s="1">
+        <f t="shared" si="0"/>
+        <v>0.30459999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3">
+        <v>9863785</v>
+      </c>
+      <c r="C31" s="1">
+        <v>8.6199999999999999E-2</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.11849999999999999</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.1293</v>
+      </c>
+      <c r="H31" s="1">
+        <f t="shared" si="0"/>
+        <v>0.33399999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H32" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H33" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H34" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H35" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H37" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H38" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H39" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H41" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H42" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H43" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H45" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H47" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H48" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H49" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H50" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H51" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H52" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H53" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H54" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H55" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H56" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H57" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H59" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H60" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H61" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H62" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H63" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H64" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H65" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H66" s="1">
+        <f t="shared" ref="H66:H104" si="1">SUM(C66:G66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H67" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H68" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H69" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H70" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H71" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H72" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H73" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H74" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H75" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H76" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H77" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H78" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H79" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H80" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H81" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H82" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H83" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H84" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H85" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H86" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H87" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H88" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H89" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H90" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H91" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H92" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H93" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H94" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H95" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H96" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H97" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H98" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H99" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H100" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H101" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H102" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H103" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H104" s="1">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>

--- a/data/burst.xlsx
+++ b/data/burst.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc6f98a884355999/pococha-burst-viewer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="297" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E22C95C-EB85-40B3-9E7B-857EEFC4353F}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152F833D-7B91-4237-8632-087CCD6F9ADC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22605" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9585" windowHeight="15390" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">まとめ!$A$1:$B$1</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
   <si>
     <t>名前</t>
   </si>
@@ -171,6 +172,10 @@
   </si>
   <si>
     <t>あいにー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GOD</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2086,9 +2091,12 @@
       <c r="E18" s="1">
         <v>0.1598</v>
       </c>
+      <c r="F18" s="1">
+        <v>0.1368</v>
+      </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
-        <v>0.44</v>
+        <v>0.57679999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -2149,9 +2157,12 @@
       <c r="E21" s="1">
         <v>0.14269999999999999</v>
       </c>
+      <c r="F21" s="1">
+        <v>0.15049999999999999</v>
+      </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
-        <v>0.39239999999999997</v>
+        <v>0.54289999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -2212,9 +2223,12 @@
       <c r="E24" s="1">
         <v>0.14699999999999999</v>
       </c>
+      <c r="F24" s="1">
+        <v>0.13700000000000001</v>
+      </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
-        <v>0.38839999999999997</v>
+        <v>0.52539999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -2296,9 +2310,12 @@
       <c r="E28" s="1">
         <v>0.11700000000000001</v>
       </c>
+      <c r="F28" s="1">
+        <v>0.1368</v>
+      </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
-        <v>0.313</v>
+        <v>0.44979999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -2365,9 +2382,24 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="1">
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.1031</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.12809999999999999</v>
+      </c>
       <c r="H32" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30169999999999997</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.4">
@@ -2800,6 +2832,294 @@
       <c r="H104" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1E47EB-7E94-4122-9C6F-6C5438828889}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="10.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3">
+        <v>11105602</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0.124</v>
+      </c>
+      <c r="D1" s="1">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="E1" s="1">
+        <v>0.1477</v>
+      </c>
+      <c r="F1" s="1">
+        <v>0.16589999999999999</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1">
+        <f>SUM(C1:G1)</f>
+        <v>0.5736</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>10616381</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.14280000000000001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.1565</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.1764</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.1847</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
+        <f>SUM(C2:G2)</f>
+        <v>0.66039999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3857497</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.13850000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.1585</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.1651</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
+        <f>SUM(C3:G3)</f>
+        <v>0.59760000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>4124528</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.1368</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.14810000000000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <f>SUM(C4:G4)</f>
+        <v>0.58260000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>11653960</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <f>SUM(C5:G5)</f>
+        <v>0.56020000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9747604</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.1613</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.18509999999999999</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <f>SUM(C6:G6)</f>
+        <v>0.66500000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>10365606</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.1459</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <f>SUM(C7:G7)</f>
+        <v>0.58310000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1">
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.1031</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <f>SUM(C8:G8)</f>
+        <v>0.30169999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3">
+        <v>6324408</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.1212</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.1285</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.14269999999999999</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.15049999999999999</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <f>SUM(C9:G9)</f>
+        <v>0.54289999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11375494</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.1191</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <f t="shared" ref="H10" si="0">SUM(C10:G10)</f>
+        <v>0.52539999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10588807</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.1021</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.1368</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <f t="shared" ref="H11" si="1">SUM(C11:G11)</f>
+        <v>0.44979999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/burst.xlsx
+++ b/data/burst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc6f98a884355999/pococha-burst-viewer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152F833D-7B91-4237-8632-087CCD6F9ADC}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5065ABDD-D378-4A82-9398-949CE7A283D1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9585" windowHeight="15390" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26295" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -625,9 +625,12 @@
       <c r="E2" s="1">
         <v>0.1734</v>
       </c>
+      <c r="F2" s="1">
+        <v>0.1988</v>
+      </c>
       <c r="H2" s="1">
         <f t="shared" ref="H2:H33" si="0">SUM(C2:G2)</f>
-        <v>0.48580000000000001</v>
+        <v>0.68459999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -646,9 +649,12 @@
       <c r="E3" s="1">
         <v>0.159</v>
       </c>
+      <c r="F3" s="1">
+        <v>0.17660000000000001</v>
+      </c>
       <c r="H3" s="1">
         <f t="shared" si="0"/>
-        <v>0.43769999999999998</v>
+        <v>0.61429999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -667,9 +673,12 @@
       <c r="E4" s="1">
         <v>0.1764</v>
       </c>
+      <c r="F4" s="1">
+        <v>0.18709999999999999</v>
+      </c>
       <c r="H4" s="1">
         <f t="shared" si="0"/>
-        <v>0.47570000000000001</v>
+        <v>0.66280000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -709,9 +718,12 @@
       <c r="E6" s="1">
         <v>0.17860000000000001</v>
       </c>
+      <c r="F6" s="1">
+        <v>0.1903</v>
+      </c>
       <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>0.47989999999999999</v>
+        <v>0.67020000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -730,9 +742,12 @@
       <c r="E7" s="1">
         <v>0.14990000000000001</v>
       </c>
+      <c r="F7" s="1">
+        <v>0.1646</v>
+      </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>0.40710000000000002</v>
+        <v>0.57169999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -751,9 +766,12 @@
       <c r="E8" s="1">
         <v>0.1772</v>
       </c>
+      <c r="F8" s="1">
+        <v>0.19139999999999999</v>
+      </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>0.48130000000000006</v>
+        <v>0.67270000000000008</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -772,9 +790,12 @@
       <c r="E9" s="1">
         <v>0.1585</v>
       </c>
+      <c r="F9" s="1">
+        <v>0.16439999999999999</v>
+      </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>0.4325</v>
+        <v>0.59689999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -793,9 +814,12 @@
       <c r="E10" s="1">
         <v>0.14810000000000001</v>
       </c>
+      <c r="F10" s="1">
+        <v>0.1638</v>
+      </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>0.42190000000000005</v>
+        <v>0.58570000000000011</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -814,9 +838,12 @@
       <c r="E11" s="1">
         <v>0.16070000000000001</v>
       </c>
+      <c r="F11" s="1">
+        <v>0.1789</v>
+      </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
-        <v>0.43709999999999999</v>
+        <v>0.61599999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -835,9 +862,12 @@
       <c r="E12" s="1">
         <v>0.15160000000000001</v>
       </c>
+      <c r="F12" s="1">
+        <v>0.14230000000000001</v>
+      </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
-        <v>0.41689999999999999</v>
+        <v>0.55920000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -856,9 +886,12 @@
       <c r="E13" s="1">
         <v>0.17</v>
       </c>
+      <c r="F13" s="1">
+        <v>0.1772</v>
+      </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
-        <v>0.46160000000000001</v>
+        <v>0.63880000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -877,9 +910,12 @@
       <c r="E14" s="1">
         <v>0.1477</v>
       </c>
+      <c r="F14" s="1">
+        <v>0.16239999999999999</v>
+      </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
-        <v>0.40770000000000001</v>
+        <v>0.57010000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -898,9 +934,12 @@
       <c r="E15" s="1">
         <v>0.12720000000000001</v>
       </c>
+      <c r="F15" s="1">
+        <v>0.1409</v>
+      </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
-        <v>0.3291</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -919,9 +958,12 @@
       <c r="E16" s="1">
         <v>0.182</v>
       </c>
+      <c r="F16" s="1">
+        <v>0.2026</v>
+      </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
-        <v>0.45710000000000001</v>
+        <v>0.65969999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -940,9 +982,12 @@
       <c r="E17" s="1">
         <v>0.1024</v>
       </c>
+      <c r="F17" s="1">
+        <v>0.152</v>
+      </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
-        <v>0.28310000000000002</v>
+        <v>0.43510000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -961,9 +1006,12 @@
       <c r="E18" s="1">
         <v>0.1598</v>
       </c>
+      <c r="F18" s="1">
+        <v>0.1779</v>
+      </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
-        <v>0.44</v>
+        <v>0.6179</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -982,9 +1030,12 @@
       <c r="E19" s="1">
         <v>0.15559999999999999</v>
       </c>
+      <c r="F19" s="1">
+        <v>0.1638</v>
+      </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
-        <v>0.40149999999999997</v>
+        <v>0.56529999999999991</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -1003,9 +1054,12 @@
       <c r="E20" s="1">
         <v>0.158</v>
       </c>
+      <c r="F20" s="1">
+        <v>0.17699999999999999</v>
+      </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
-        <v>0.40860000000000007</v>
+        <v>0.58560000000000012</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1024,9 +1078,12 @@
       <c r="E21" s="1">
         <v>0.14269999999999999</v>
       </c>
+      <c r="F21" s="1">
+        <v>0.1492</v>
+      </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
-        <v>0.39239999999999997</v>
+        <v>0.54159999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1045,9 +1102,12 @@
       <c r="E22" s="1">
         <v>0.1482</v>
       </c>
+      <c r="F22" s="1">
+        <v>0.17299999999999999</v>
+      </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
-        <v>0.40620000000000001</v>
+        <v>0.57919999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -1066,9 +1126,12 @@
       <c r="E23" s="1">
         <v>0.14549999999999999</v>
       </c>
+      <c r="F23" s="1">
+        <v>0.14449999999999999</v>
+      </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
-        <v>0.37209999999999999</v>
+        <v>0.51659999999999995</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1087,9 +1150,12 @@
       <c r="E24" s="1">
         <v>0.14699999999999999</v>
       </c>
+      <c r="F24" s="1">
+        <v>0.16220000000000001</v>
+      </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
-        <v>0.38839999999999997</v>
+        <v>0.55059999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1108,9 +1174,12 @@
       <c r="E25" s="1">
         <v>9.0200000000000002E-2</v>
       </c>
+      <c r="F25" s="1">
+        <v>0.1045</v>
+      </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
-        <v>0.26629999999999998</v>
+        <v>0.37079999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -1129,9 +1198,12 @@
       <c r="E26" s="1">
         <v>0.1002</v>
       </c>
+      <c r="F26" s="1">
+        <v>9.3799999999999994E-2</v>
+      </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
-        <v>0.3241</v>
+        <v>0.41789999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -1150,9 +1222,12 @@
       <c r="E27" s="1">
         <v>0.1318</v>
       </c>
+      <c r="F27" s="1">
+        <v>0.16669999999999999</v>
+      </c>
       <c r="H27" s="1">
         <f t="shared" si="0"/>
-        <v>0.34609999999999996</v>
+        <v>0.51279999999999992</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -1171,9 +1246,12 @@
       <c r="E28" s="1">
         <v>0.11700000000000001</v>
       </c>
+      <c r="F28" s="1">
+        <v>0.1424</v>
+      </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
-        <v>0.313</v>
+        <v>0.45540000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -1213,9 +1291,12 @@
       <c r="E30" s="1">
         <v>0.1303</v>
       </c>
+      <c r="F30" s="1">
+        <v>0.14940000000000001</v>
+      </c>
       <c r="H30" s="1">
         <f t="shared" si="0"/>
-        <v>0.30459999999999998</v>
+        <v>0.45399999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -1234,9 +1315,12 @@
       <c r="E31" s="1">
         <v>0.1293</v>
       </c>
+      <c r="F31" s="1">
+        <v>0.16020000000000001</v>
+      </c>
       <c r="H31" s="1">
         <f t="shared" si="0"/>
-        <v>0.33399999999999996</v>
+        <v>0.49419999999999997</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -2870,7 +2954,7 @@
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1">
-        <f>SUM(C1:G1)</f>
+        <f t="shared" ref="H1:H9" si="0">SUM(C1:G1)</f>
         <v>0.5736</v>
       </c>
     </row>
@@ -2895,7 +2979,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1">
-        <f>SUM(C2:G2)</f>
+        <f t="shared" si="0"/>
         <v>0.66039999999999999</v>
       </c>
     </row>
@@ -2920,7 +3004,7 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
-        <f>SUM(C3:G3)</f>
+        <f t="shared" si="0"/>
         <v>0.59760000000000002</v>
       </c>
     </row>
@@ -2945,7 +3029,7 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1">
-        <f>SUM(C4:G4)</f>
+        <f t="shared" si="0"/>
         <v>0.58260000000000001</v>
       </c>
     </row>
@@ -2970,7 +3054,7 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1">
-        <f>SUM(C5:G5)</f>
+        <f t="shared" si="0"/>
         <v>0.56020000000000003</v>
       </c>
     </row>
@@ -2995,7 +3079,7 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
-        <f>SUM(C6:G6)</f>
+        <f t="shared" si="0"/>
         <v>0.66500000000000004</v>
       </c>
     </row>
@@ -3020,7 +3104,7 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
-        <f>SUM(C7:G7)</f>
+        <f t="shared" si="0"/>
         <v>0.58310000000000006</v>
       </c>
     </row>
@@ -3043,7 +3127,7 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1">
-        <f>SUM(C8:G8)</f>
+        <f t="shared" si="0"/>
         <v>0.30169999999999997</v>
       </c>
     </row>
@@ -3068,7 +3152,7 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
-        <f>SUM(C9:G9)</f>
+        <f t="shared" si="0"/>
         <v>0.54289999999999994</v>
       </c>
     </row>
@@ -3093,7 +3177,7 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1">
-        <f t="shared" ref="H10" si="0">SUM(C10:G10)</f>
+        <f t="shared" ref="H10" si="1">SUM(C10:G10)</f>
         <v>0.52539999999999998</v>
       </c>
     </row>
@@ -3118,7 +3202,7 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
-        <f t="shared" ref="H11" si="1">SUM(C11:G11)</f>
+        <f t="shared" ref="H11" si="2">SUM(C11:G11)</f>
         <v>0.44979999999999998</v>
       </c>
     </row>

--- a/data/burst.xlsx
+++ b/data/burst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc6f98a884355999/pococha-burst-viewer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5065ABDD-D378-4A82-9398-949CE7A283D1}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="8_{A7CB9F1E-1B4A-400C-9D13-17105FF6455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2EB6D24-2B1E-4FAA-8CCB-FC224C30BE3F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="26295" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,9 +697,12 @@
       <c r="E5" s="1">
         <v>0.1459</v>
       </c>
+      <c r="F5" s="1">
+        <v>0.16300000000000001</v>
+      </c>
       <c r="H5" s="1">
         <f t="shared" si="0"/>
-        <v>0.41710000000000003</v>
+        <v>0.58010000000000006</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1268,6 +1271,9 @@
         <v>6.2100000000000002E-2</v>
       </c>
       <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
